--- a/excel/ShopData.xlsx
+++ b/excel/ShopData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DCA63A-8B8C-E242-9EA0-E19982C770C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E129175-E9CB-6B45-B98B-C740A22A3D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9580" yWindow="4020" windowWidth="19820" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopInfo" sheetId="1" r:id="rId1"/>
@@ -532,7 +532,7 @@
         <v>800</v>
       </c>
       <c r="C3" s="8">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>10</v>
@@ -546,7 +546,7 @@
         <v>800</v>
       </c>
       <c r="C4" s="8">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>9</v>
@@ -560,7 +560,7 @@
         <v>800</v>
       </c>
       <c r="C5" s="8">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>12</v>

--- a/excel/ShopData.xlsx
+++ b/excel/ShopData.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E129175-E9CB-6B45-B98B-C740A22A3D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DFEB87-5C32-A04B-97EA-6AB21CC9C600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1800" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopInfo" sheetId="1" r:id="rId1"/>
+    <sheet name="ShopProduct" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
   <si>
     <t>int;key</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -132,6 +133,450 @@
   </si>
   <si>
     <t>BeddingShop</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마도구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킨1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마도구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킨2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플레이어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가루</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노랑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕가게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <t>ProductItemId</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxPurchasableQuantity</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum&lt;RequirementType&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SaleRequirementType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SaleRequirementValues</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PriceQuantity</t>
+  </si>
+  <si>
+    <t>PriceItemId</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>솔라뱅크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화폐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <t>ActivateDuration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200, 1500</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomMinStockQuantity</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomMaxStockQuantity</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -142,7 +587,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$₩-412]#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -195,8 +640,16 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -213,6 +666,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEFEFEF"/>
         <bgColor rgb="FFEFEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF2CD"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -254,7 +713,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -269,6 +728,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -575,4 +1036,190 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73322D1C-5C6E-0B42-8B10-D10F8B7E4791}">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <cols>
+    <col min="2" max="3" width="26.33203125" customWidth="1"/>
+    <col min="4" max="4" width="23.5" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15">
+      <c r="A3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3">
+        <v>149000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
+      <c r="A4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="10">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4">
+        <v>129000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
+      <c r="A5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="10">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15">
+      <c r="A6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="10">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15">
+      <c r="A7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="10">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7">
+        <v>5000</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/excel/ShopData.xlsx
+++ b/excel/ShopData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DFEB87-5C32-A04B-97EA-6AB21CC9C600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC28611-8F14-3C49-A4D7-0B390DB879AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1800" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1800" windowWidth="24120" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopInfo" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
   <si>
     <t>int;key</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -577,6 +577,18 @@
   </si>
   <si>
     <t>RandomMaxStockQuantity</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinigameType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum&lt;MinigameType&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PowderPortal</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -970,6 +982,9 @@
       <c r="D1" s="9" t="s">
         <v>8</v>
       </c>
+      <c r="E1" s="9" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
@@ -984,6 +999,9 @@
       <c r="D2" s="8" t="s">
         <v>11</v>
       </c>
+      <c r="E2" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="15">
       <c r="A3" s="6" t="s">
@@ -997,6 +1015,9 @@
       </c>
       <c r="D3" s="8" t="s">
         <v>10</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">

--- a/excel/ShopData.xlsx
+++ b/excel/ShopData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC28611-8F14-3C49-A4D7-0B390DB879AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90294AF-DAEC-224C-A3D2-468B889240CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1800" windowWidth="24120" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1800" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopInfo" sheetId="1" r:id="rId1"/>
@@ -502,10 +502,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>List&lt;int&gt;</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>SaleRequirementValues</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -589,6 +585,10 @@
   </si>
   <si>
     <t>PowderPortal</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;int&gt;</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -983,7 +983,7 @@
         <v>8</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
@@ -1000,7 +1000,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
@@ -1017,7 +1017,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
@@ -1092,7 +1092,7 @@
         <v>21</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>2</v>
@@ -1109,10 +1109,10 @@
         <v>19</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>31</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>20</v>
@@ -1121,13 +1121,13 @@
         <v>22</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
         <v>24</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15">
@@ -1144,13 +1144,13 @@
         <v>3</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>29</v>
-      </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3">
         <v>149000</v>
@@ -1170,7 +1170,7 @@
         <v>4</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I4">
         <v>129000</v>
@@ -1193,7 +1193,7 @@
         <v>5</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5">
         <v>1400</v>
@@ -1213,7 +1213,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I6">
         <v>1500</v>
@@ -1233,7 +1233,7 @@
         <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7">
         <v>5000</v>

--- a/excel/ShopData.xlsx
+++ b/excel/ShopData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90294AF-DAEC-224C-A3D2-468B889240CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BB53441-4082-F549-8757-70106281E240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1800" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -588,7 +588,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>list&lt;int&gt;</t>
+    <t>list&lt;int&gt;d</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>

--- a/excel/ShopData.xlsx
+++ b/excel/ShopData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BB53441-4082-F549-8757-70106281E240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0448FD39-981F-FB49-B738-4FB219A9EA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1800" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -588,7 +588,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>list&lt;int&gt;d</t>
+    <t>list&lt;int&gt;</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>

--- a/excel/ShopData.xlsx
+++ b/excel/ShopData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0448FD39-981F-FB49-B738-4FB219A9EA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4FD945-3313-7C4F-B8D4-1342407CCB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1800" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1780" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopInfo" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t>int;key</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -568,14 +568,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>RandomMinStockQuantity</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>RandomMaxStockQuantity</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>MinigameType</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -589,6 +581,10 @@
   </si>
   <si>
     <t>list&lt;int&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RefreshAmount</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -983,7 +979,7 @@
         <v>8</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
@@ -1000,7 +996,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
@@ -1017,7 +1013,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
@@ -1061,18 +1057,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73322D1C-5C6E-0B42-8B10-D10F8B7E4791}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="3" width="26.33203125" customWidth="1"/>
-    <col min="4" max="4" width="23.5" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.5" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="8" t="s">
         <v>2</v>
       </c>
@@ -1086,22 +1082,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>2</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>2</v>
-      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:8">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -1109,133 +1102,115 @@
         <v>19</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15">
+    <row r="3" spans="1:8" ht="15">
       <c r="A3" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H3" t="s">
+      <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="I3">
+      <c r="H3">
         <v>149000</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15">
+    <row r="4" spans="1:8" ht="15">
       <c r="A4" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4">
         <v>2</v>
       </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="G4" t="s">
         <v>26</v>
       </c>
-      <c r="I4">
+      <c r="H4">
         <v>129000</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15">
+    <row r="5" spans="1:8" ht="15">
       <c r="A5" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5">
         <v>3</v>
       </c>
       <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
         <v>5</v>
       </c>
-      <c r="H5" t="s">
+      <c r="G5" t="s">
         <v>26</v>
       </c>
-      <c r="I5">
+      <c r="H5">
         <v>1400</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15">
+    <row r="6" spans="1:8" ht="15">
       <c r="A6" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6">
         <v>4</v>
       </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="G6" t="s">
         <v>26</v>
       </c>
-      <c r="I6">
+      <c r="H6">
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15">
+    <row r="7" spans="1:8" ht="15">
       <c r="A7" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="10">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
         <v>26</v>
       </c>
-      <c r="I7">
+      <c r="H7">
         <v>5000</v>
       </c>
     </row>

--- a/excel/ShopData.xlsx
+++ b/excel/ShopData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4FD945-3313-7C4F-B8D4-1342407CCB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A504190-3E90-164A-841C-E875CAD13DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1780" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <t>int;key</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -586,6 +586,136 @@
   <si>
     <t>RefreshAmount</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProductId</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕가게_상품_01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕가게_상품_02]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕가게_상품_03]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕가게_상품_04]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕가게_상품_05]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
   </si>
 </sst>
 </file>
@@ -1057,23 +1187,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73322D1C-5C6E-0B42-8B10-D10F8B7E4791}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="26.33203125" customWidth="1"/>
-    <col min="3" max="3" width="23.5" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" customWidth="1"/>
+    <col min="4" max="4" width="23.5" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>2</v>
@@ -1082,135 +1213,156 @@
         <v>2</v>
       </c>
       <c r="E1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>2</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>2</v>
       </c>
+      <c r="I1" s="8" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15">
+    <row r="3" spans="1:9" ht="15">
       <c r="A3" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>26</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>149000</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15">
+    <row r="4" spans="1:9" ht="15">
       <c r="A4" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>2</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>26</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>129000</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15">
+    <row r="5" spans="1:9" ht="15">
       <c r="A5" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>3</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>26</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>1400</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15">
+    <row r="6" spans="1:9" ht="15">
       <c r="A6" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>4</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>26</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>1500</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15">
+    <row r="7" spans="1:9" ht="15">
       <c r="A7" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>5</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>26</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>5000</v>
       </c>
     </row>

--- a/excel/ShopData.xlsx
+++ b/excel/ShopData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A504190-3E90-164A-841C-E875CAD13DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E895E6F-35F9-5F4A-822F-820AC7D130E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1780" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
   <si>
     <t>int;key</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -716,6 +716,242 @@
       </rPr>
       <t/>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸_상품_01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_02]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_03]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_04]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_05]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1187,7 +1423,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73322D1C-5C6E-0B42-8B10-D10F8B7E4791}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="17.5" customWidth="1"/>
@@ -1366,6 +1602,115 @@
         <v>5000</v>
       </c>
     </row>
+    <row r="8" spans="1:9" ht="15">
+      <c r="A8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>149000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15">
+      <c r="A9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9">
+        <v>129000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15">
+      <c r="A10" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15">
+      <c r="A11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="H11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15">
+      <c r="A12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12">
+        <v>5000</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/ShopData.xlsx
+++ b/excel/ShopData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E895E6F-35F9-5F4A-822F-820AC7D130E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE920BC-AD63-B743-B691-B81A9C4485AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1780" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3860" yWindow="1780" windowWidth="15260" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopInfo" sheetId="1" r:id="rId1"/>
@@ -21,22 +21,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="67">
   <si>
     <t>int;key</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ShopId</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>StartTime</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -61,7 +61,7 @@
       </rPr>
       <t>]</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -86,7 +86,7 @@
       </rPr>
       <t>]</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -111,15 +111,15 @@
       </rPr>
       <t>]</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EndTime</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enum&lt;ShopType&gt;</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>PowderShop</t>
@@ -129,11 +129,11 @@
   </si>
   <si>
     <t>ShopType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BeddingShop</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -487,30 +487,30 @@
   </si>
   <si>
     <t>ProductItemId</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MaxPurchasableQuantity</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enum&lt;RequirementType&gt;</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SaleRequirementType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SaleRequirementValues</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>PriceQuantity</t>
   </si>
   <si>
     <t>PriceItemId</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -561,35 +561,35 @@
   </si>
   <si>
     <t>ActivateDuration</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>1200, 1500</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MinigameType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enum&lt;MinigameType&gt;</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>PowderPortal</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>list&lt;int&gt;</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>RefreshAmount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ProductId</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -615,7 +615,7 @@
       </rPr>
       <t>]</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -741,7 +741,7 @@
       </rPr>
       <t>]</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -767,7 +767,7 @@
       </rPr>
       <t>]</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -813,7 +813,7 @@
       </rPr>
       <t>_02]</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -859,7 +859,7 @@
       </rPr>
       <t>_03]</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -905,7 +905,7 @@
       </rPr>
       <t>_04]</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -951,7 +951,678 @@
       </rPr>
       <t>_05]</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸_상품_06]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_07]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_08]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_09]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>[페로페로_향수]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회복약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>지침</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회복약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>농땡이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>파우더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>캐슬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕가게_상품_06]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕가게_상품_07]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕가게_상품_08]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕가게_상품_09]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜솜가루</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜뭉치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>씨앗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바삭바삭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꿈뭉치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[마도구_스틱_솜사탕가게_스킨1]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[사역마_회복약3]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[오로라_파르페]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[미카_포토카드]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>솜솜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>보틀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탈것_솜사탕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -961,11 +1632,19 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$₩-412]#,##0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1087,23 +1766,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1416,14 +2096,14 @@
       <c r="E12" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73322D1C-5C6E-0B42-8B10-D10F8B7E4791}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="17.5" customWidth="1"/>
@@ -1500,8 +2180,8 @@
       <c r="B3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>13</v>
+      <c r="C3" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1526,8 +2206,8 @@
       <c r="B4" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>14</v>
+      <c r="C4" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -1546,8 +2226,8 @@
       <c r="B5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>15</v>
+      <c r="C5" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -1569,8 +2249,8 @@
       <c r="B6" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>16</v>
+      <c r="C6" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -1589,8 +2269,8 @@
       <c r="B7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>17</v>
+      <c r="C7" t="s">
+        <v>65</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1604,91 +2284,82 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" s="10" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>13</v>
+        <v>54</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H8" t="s">
         <v>26</v>
       </c>
       <c r="I8">
-        <v>149000</v>
+        <v>129000</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" s="10" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>14</v>
+        <v>55</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H9" t="s">
         <v>26</v>
       </c>
       <c r="I9">
-        <v>129000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" s="10" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>15</v>
+        <v>56</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H10" t="s">
         <v>26</v>
       </c>
       <c r="I10">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" s="10" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>16</v>
+        <v>57</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H11" t="s">
         <v>26</v>
       </c>
       <c r="I11">
-        <v>1500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1696,23 +2367,192 @@
         <v>40</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="H12" t="s">
         <v>26</v>
       </c>
       <c r="I12">
+        <v>149000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15">
+      <c r="A13" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="H13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13">
+        <v>129000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15">
+      <c r="A14" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15">
+      <c r="A15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="H15" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15">
+      <c r="A16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15">
+      <c r="A17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="H17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17">
+        <v>129000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="16">
+      <c r="A18" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18">
+        <v>7</v>
+      </c>
+      <c r="H18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="16">
+      <c r="A19" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19">
+        <v>8</v>
+      </c>
+      <c r="H19" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="16">
+      <c r="A20" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20">
+        <v>9</v>
+      </c>
+      <c r="H20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20">
         <v>5000</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>